--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3524"/>
+  <dimension ref="A1:F3534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87248,6 +87248,306 @@
         </is>
       </c>
     </row>
+    <row r="3525">
+      <c r="A3525" t="inlineStr">
+        <is>
+          <t>bb56991e-f857-4c6a-a410-2793fa6bda64</t>
+        </is>
+      </c>
+      <c r="B3525" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3525" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:45:03.128Z</t>
+        </is>
+      </c>
+      <c r="D3525" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3525" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3525" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3526">
+      <c r="A3526" t="inlineStr">
+        <is>
+          <t>157f8fdc-0a1d-4dd4-b74d-b7fab8286c92</t>
+        </is>
+      </c>
+      <c r="B3526" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3526" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:18:21.910Z</t>
+        </is>
+      </c>
+      <c r="D3526" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3526" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3526" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3527">
+      <c r="A3527" t="inlineStr">
+        <is>
+          <t>979575dd-c7f7-4e4e-96de-c7073e00b177</t>
+        </is>
+      </c>
+      <c r="B3527" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3527" t="inlineStr">
+        <is>
+          <t>2026-09-12T02:37:55.977Z</t>
+        </is>
+      </c>
+      <c r="D3527" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3527" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3527" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3528">
+      <c r="A3528" t="inlineStr">
+        <is>
+          <t>e69c04cf-89dc-4682-9b13-995854517c96</t>
+        </is>
+      </c>
+      <c r="B3528" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3528" t="inlineStr">
+        <is>
+          <t>2026-09-12T05:32:18.979Z</t>
+        </is>
+      </c>
+      <c r="D3528" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3528" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3528" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3529">
+      <c r="A3529" t="inlineStr">
+        <is>
+          <t>43adf53c-d6eb-4cb1-9964-f4a26136a4b1</t>
+        </is>
+      </c>
+      <c r="B3529" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3529" t="inlineStr">
+        <is>
+          <t>2026-09-12T06:11:24.234Z</t>
+        </is>
+      </c>
+      <c r="D3529" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3529" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3529" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3530">
+      <c r="A3530" t="inlineStr">
+        <is>
+          <t>ef1df576-4d1b-4e2d-9f98-c71510d73448</t>
+        </is>
+      </c>
+      <c r="B3530" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3530" t="inlineStr">
+        <is>
+          <t>2026-09-12T16:01:28.539Z</t>
+        </is>
+      </c>
+      <c r="D3530" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3530" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3530" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3531">
+      <c r="A3531" t="inlineStr">
+        <is>
+          <t>82d9f241-212e-4e0e-8d7e-dc5893243c6f</t>
+        </is>
+      </c>
+      <c r="B3531" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3531" t="inlineStr">
+        <is>
+          <t>2026-09-12T20:13:17.795Z</t>
+        </is>
+      </c>
+      <c r="D3531" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3531" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3531" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3532">
+      <c r="A3532" t="inlineStr">
+        <is>
+          <t>c9f81237-9c5c-4bfe-82be-1c6d8260f65f</t>
+        </is>
+      </c>
+      <c r="B3532" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3532" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:48:03.288Z</t>
+        </is>
+      </c>
+      <c r="D3532" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3532" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3532" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3533">
+      <c r="A3533" t="inlineStr">
+        <is>
+          <t>621c21c0-e1c3-4496-97cf-3df3173d6bc3</t>
+        </is>
+      </c>
+      <c r="B3533" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3533" t="inlineStr">
+        <is>
+          <t>2026-09-12T23:07:33.589Z</t>
+        </is>
+      </c>
+      <c r="D3533" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3533" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3533" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3534">
+      <c r="A3534" t="inlineStr">
+        <is>
+          <t>11412445-0d27-40f0-90a6-41d6489edce3</t>
+        </is>
+      </c>
+      <c r="B3534" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3534" t="inlineStr">
+        <is>
+          <t>2026-09-12T23:10:26.712Z</t>
+        </is>
+      </c>
+      <c r="D3534" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3534" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3534" t="inlineStr">
+        <is>
+          <t>Weapons Offense (Guns/Shots Fired)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3534"/>
+  <dimension ref="A1:F3538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87548,6 +87548,126 @@
         </is>
       </c>
     </row>
+    <row r="3535">
+      <c r="A3535" t="inlineStr">
+        <is>
+          <t>f5e7cbf7-3a52-44bb-bbb1-1611084964b9</t>
+        </is>
+      </c>
+      <c r="B3535" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3535" t="inlineStr">
+        <is>
+          <t>2026-09-13T00:15:37.383Z</t>
+        </is>
+      </c>
+      <c r="D3535" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3535" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3535" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3536">
+      <c r="A3536" t="inlineStr">
+        <is>
+          <t>f21f30cb-6d87-449d-a8bb-224a5ca5bd49</t>
+        </is>
+      </c>
+      <c r="B3536" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3536" t="inlineStr">
+        <is>
+          <t>2026-09-13T01:21:31.602Z</t>
+        </is>
+      </c>
+      <c r="D3536" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3536" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3536" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3537">
+      <c r="A3537" t="inlineStr">
+        <is>
+          <t>9c009027-c957-4b56-9add-69f4e11f8fb0</t>
+        </is>
+      </c>
+      <c r="B3537" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3537" t="inlineStr">
+        <is>
+          <t>2026-09-13T22:26:39.205Z</t>
+        </is>
+      </c>
+      <c r="D3537" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3537" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3537" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3538">
+      <c r="A3538" t="inlineStr">
+        <is>
+          <t>8ad0f895-bb90-49ec-b0fa-fe556a4e0f19</t>
+        </is>
+      </c>
+      <c r="B3538" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3538" t="inlineStr">
+        <is>
+          <t>2026-09-13T23:49:33.039Z</t>
+        </is>
+      </c>
+      <c r="D3538" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3538" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3538" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3538"/>
+  <dimension ref="A1:F3553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87668,6 +87668,456 @@
         </is>
       </c>
     </row>
+    <row r="3539">
+      <c r="A3539" t="inlineStr">
+        <is>
+          <t>acdbabc4-c488-4066-a718-c406bced579a</t>
+        </is>
+      </c>
+      <c r="B3539" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3539" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:43:05.179Z</t>
+        </is>
+      </c>
+      <c r="D3539" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3539" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3539" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3540">
+      <c r="A3540" t="inlineStr">
+        <is>
+          <t>39bbccc2-6ead-405a-aa3e-f4007370a9e2</t>
+        </is>
+      </c>
+      <c r="B3540" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3540" t="inlineStr">
+        <is>
+          <t>2026-09-14T03:11:00.365Z</t>
+        </is>
+      </c>
+      <c r="D3540" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3540" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3540" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3541">
+      <c r="A3541" t="inlineStr">
+        <is>
+          <t>05c93911-1a30-4f4f-bad1-f2fc3dae7a72</t>
+        </is>
+      </c>
+      <c r="B3541" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3541" t="inlineStr">
+        <is>
+          <t>2026-09-14T04:10:14.682Z</t>
+        </is>
+      </c>
+      <c r="D3541" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3541" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3541" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3542">
+      <c r="A3542" t="inlineStr">
+        <is>
+          <t>3dcc4818-b00f-4e43-9979-76ec5b7d0f49</t>
+        </is>
+      </c>
+      <c r="B3542" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3542" t="inlineStr">
+        <is>
+          <t>2026-09-14T06:20:10.164Z</t>
+        </is>
+      </c>
+      <c r="D3542" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3542" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3542" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3543">
+      <c r="A3543" t="inlineStr">
+        <is>
+          <t>da1260a3-9e0e-46fa-9c7d-f5bda0f318ac</t>
+        </is>
+      </c>
+      <c r="B3543" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3543" t="inlineStr">
+        <is>
+          <t>2026-09-14T06:42:03.589Z</t>
+        </is>
+      </c>
+      <c r="D3543" t="n">
+        <v>510</v>
+      </c>
+      <c r="E3543" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3543" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3544">
+      <c r="A3544" t="inlineStr">
+        <is>
+          <t>9a2bcafb-9b22-4c0c-b93f-ab981f3b61cb</t>
+        </is>
+      </c>
+      <c r="B3544" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3544" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:01:36.588Z</t>
+        </is>
+      </c>
+      <c r="D3544" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3544" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3544" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3545">
+      <c r="A3545" t="inlineStr">
+        <is>
+          <t>b038c1c5-1990-4472-af26-e0276658fda8</t>
+        </is>
+      </c>
+      <c r="B3545" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3545" t="inlineStr">
+        <is>
+          <t>2026-09-14T07:05:34.100Z</t>
+        </is>
+      </c>
+      <c r="D3545" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3545" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3545" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3546">
+      <c r="A3546" t="inlineStr">
+        <is>
+          <t>dc414994-7185-4e35-9a87-759d3e58e70b</t>
+        </is>
+      </c>
+      <c r="B3546" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3546" t="inlineStr">
+        <is>
+          <t>2026-09-14T16:12:39.923Z</t>
+        </is>
+      </c>
+      <c r="D3546" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3546" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3546" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3547">
+      <c r="A3547" t="inlineStr">
+        <is>
+          <t>45f85c61-e5f4-4c88-a594-c24973f3c698</t>
+        </is>
+      </c>
+      <c r="B3547" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3547" t="inlineStr">
+        <is>
+          <t>2026-09-14T17:59:09.306Z</t>
+        </is>
+      </c>
+      <c r="D3547" t="n">
+        <v>543</v>
+      </c>
+      <c r="E3547" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3547" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3548">
+      <c r="A3548" t="inlineStr">
+        <is>
+          <t>e922c3c6-3951-4a5f-b167-96565c0eda42</t>
+        </is>
+      </c>
+      <c r="B3548" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3548" t="inlineStr">
+        <is>
+          <t>2026-09-14T20:45:48.133Z</t>
+        </is>
+      </c>
+      <c r="D3548" t="n">
+        <v>542</v>
+      </c>
+      <c r="E3548" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3548" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3549">
+      <c r="A3549" t="inlineStr">
+        <is>
+          <t>13adef70-a397-4743-958d-55a383561e8a</t>
+        </is>
+      </c>
+      <c r="B3549" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3549" t="inlineStr">
+        <is>
+          <t>2026-09-14T21:57:58.521Z</t>
+        </is>
+      </c>
+      <c r="D3549" t="n">
+        <v>542</v>
+      </c>
+      <c r="E3549" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3549" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3550">
+      <c r="A3550" t="inlineStr">
+        <is>
+          <t>0c2c6391-bba5-41af-af50-b959704df69c</t>
+        </is>
+      </c>
+      <c r="B3550" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3550" t="inlineStr">
+        <is>
+          <t>2026-09-14T21:58:14.711Z</t>
+        </is>
+      </c>
+      <c r="D3550" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3550" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3550" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3551">
+      <c r="A3551" t="inlineStr">
+        <is>
+          <t>a754227d-3280-4c0a-9c6f-8be627f69eb4</t>
+        </is>
+      </c>
+      <c r="B3551" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3551" t="inlineStr">
+        <is>
+          <t>2026-09-14T22:00:47.678Z</t>
+        </is>
+      </c>
+      <c r="D3551" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3551" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3551" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3552">
+      <c r="A3552" t="inlineStr">
+        <is>
+          <t>413744bd-dfa4-4a81-b664-71f197ed6f78</t>
+        </is>
+      </c>
+      <c r="B3552" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3552" t="inlineStr">
+        <is>
+          <t>2026-09-14T22:13:40.152Z</t>
+        </is>
+      </c>
+      <c r="D3552" t="n">
+        <v>542</v>
+      </c>
+      <c r="E3552" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3552" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3553">
+      <c r="A3553" t="inlineStr">
+        <is>
+          <t>34c1f4f0-5804-41b3-8f41-78144f2a5de9</t>
+        </is>
+      </c>
+      <c r="B3553" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3553" t="inlineStr">
+        <is>
+          <t>2026-09-14T22:20:08.061Z</t>
+        </is>
+      </c>
+      <c r="D3553" t="n">
+        <v>499</v>
+      </c>
+      <c r="E3553" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3553" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3553"/>
+  <dimension ref="A1:F3573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88118,6 +88118,606 @@
         </is>
       </c>
     </row>
+    <row r="3554">
+      <c r="A3554" t="inlineStr">
+        <is>
+          <t>949742cb-824e-4773-95fa-3b9d6c275bf7</t>
+        </is>
+      </c>
+      <c r="B3554" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3554" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:26:12.958Z</t>
+        </is>
+      </c>
+      <c r="D3554" t="n">
+        <v>542</v>
+      </c>
+      <c r="E3554" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3554" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3555">
+      <c r="A3555" t="inlineStr">
+        <is>
+          <t>1e43da95-065b-4130-9cc4-2a29964bc1b1</t>
+        </is>
+      </c>
+      <c r="B3555" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3555" t="inlineStr">
+        <is>
+          <t>2026-09-15T01:33:56.669Z</t>
+        </is>
+      </c>
+      <c r="D3555" t="n">
+        <v>542</v>
+      </c>
+      <c r="E3555" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3555" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3556">
+      <c r="A3556" t="inlineStr">
+        <is>
+          <t>36864929-4154-4209-8068-8ba1d7466610</t>
+        </is>
+      </c>
+      <c r="B3556" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3556" t="inlineStr">
+        <is>
+          <t>2026-09-15T03:26:25.054Z</t>
+        </is>
+      </c>
+      <c r="D3556" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3556" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3556" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3557">
+      <c r="A3557" t="inlineStr">
+        <is>
+          <t>700f44ac-c47d-4cb8-8b89-6dec1030bf5e</t>
+        </is>
+      </c>
+      <c r="B3557" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3557" t="inlineStr">
+        <is>
+          <t>2026-09-15T04:12:36.570Z</t>
+        </is>
+      </c>
+      <c r="D3557" t="n">
+        <v>513</v>
+      </c>
+      <c r="E3557" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3557" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3558">
+      <c r="A3558" t="inlineStr">
+        <is>
+          <t>b7d4b40b-9d0e-4052-9e1a-7b26c081aa67</t>
+        </is>
+      </c>
+      <c r="B3558" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3558" t="inlineStr">
+        <is>
+          <t>2026-09-15T07:16:41.361Z</t>
+        </is>
+      </c>
+      <c r="D3558" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3558" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3558" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3559">
+      <c r="A3559" t="inlineStr">
+        <is>
+          <t>b6165f71-7e46-4484-89bb-653194bf2feb</t>
+        </is>
+      </c>
+      <c r="B3559" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3559" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:08:23.188Z</t>
+        </is>
+      </c>
+      <c r="D3559" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3559" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3559" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3560">
+      <c r="A3560" t="inlineStr">
+        <is>
+          <t>dea52526-34a8-476a-8d68-89f7d57ccb7b</t>
+        </is>
+      </c>
+      <c r="B3560" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3560" t="inlineStr">
+        <is>
+          <t>2026-09-15T09:18:03.192Z</t>
+        </is>
+      </c>
+      <c r="D3560" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3560" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3560" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3561">
+      <c r="A3561" t="inlineStr">
+        <is>
+          <t>c7b1a747-5277-4a58-bfa2-74955ff386cb</t>
+        </is>
+      </c>
+      <c r="B3561" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3561" t="inlineStr">
+        <is>
+          <t>2026-09-15T10:01:18.807Z</t>
+        </is>
+      </c>
+      <c r="D3561" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3561" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3561" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3562">
+      <c r="A3562" t="inlineStr">
+        <is>
+          <t>bb43a116-de3d-47d4-a522-31067bf0c784</t>
+        </is>
+      </c>
+      <c r="B3562" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3562" t="inlineStr">
+        <is>
+          <t>2026-09-15T10:01:28.268Z</t>
+        </is>
+      </c>
+      <c r="D3562" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3562" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3562" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3563">
+      <c r="A3563" t="inlineStr">
+        <is>
+          <t>2068125d-b71d-4707-9fd1-70be39ffe12e</t>
+        </is>
+      </c>
+      <c r="B3563" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3563" t="inlineStr">
+        <is>
+          <t>2026-09-15T11:45:43.266Z</t>
+        </is>
+      </c>
+      <c r="D3563" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3563" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3563" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3564">
+      <c r="A3564" t="inlineStr">
+        <is>
+          <t>145348f5-5b93-42e4-b11f-26132c5f2d88</t>
+        </is>
+      </c>
+      <c r="B3564" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3564" t="inlineStr">
+        <is>
+          <t>2026-09-15T11:46:10.932Z</t>
+        </is>
+      </c>
+      <c r="D3564" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3564" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3564" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3565">
+      <c r="A3565" t="inlineStr">
+        <is>
+          <t>6c8eb05a-24c2-41ac-a03b-21aaf18be7fb</t>
+        </is>
+      </c>
+      <c r="B3565" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3565" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:10:30.928Z</t>
+        </is>
+      </c>
+      <c r="D3565" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3565" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3565" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3566">
+      <c r="A3566" t="inlineStr">
+        <is>
+          <t>4c86ec8a-9be9-4ac0-b13d-1217a8c59a9f</t>
+        </is>
+      </c>
+      <c r="B3566" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3566" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:10:39.316Z</t>
+        </is>
+      </c>
+      <c r="D3566" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3566" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3566" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3567">
+      <c r="A3567" t="inlineStr">
+        <is>
+          <t>447ed1f1-f77e-4e21-9b5f-6ab6b87a0be6</t>
+        </is>
+      </c>
+      <c r="B3567" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3567" t="inlineStr">
+        <is>
+          <t>2026-09-15T16:48:36.890Z</t>
+        </is>
+      </c>
+      <c r="D3567" t="n">
+        <v>498</v>
+      </c>
+      <c r="E3567" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3567" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3568">
+      <c r="A3568" t="inlineStr">
+        <is>
+          <t>3917aa46-bdac-4140-a980-397262c18b06</t>
+        </is>
+      </c>
+      <c r="B3568" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3568" t="inlineStr">
+        <is>
+          <t>2026-09-15T18:14:09.995Z</t>
+        </is>
+      </c>
+      <c r="D3568" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3568" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3568" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3569">
+      <c r="A3569" t="inlineStr">
+        <is>
+          <t>acc5f4a1-deca-4e60-88cc-2745bc59b7d3</t>
+        </is>
+      </c>
+      <c r="B3569" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3569" t="inlineStr">
+        <is>
+          <t>2026-09-15T19:01:52.004Z</t>
+        </is>
+      </c>
+      <c r="D3569" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3569" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3569" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3570">
+      <c r="A3570" t="inlineStr">
+        <is>
+          <t>a22b0c2d-e5d8-4003-8fff-28a038b933ef</t>
+        </is>
+      </c>
+      <c r="B3570" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3570" t="inlineStr">
+        <is>
+          <t>2026-09-15T21:17:54.309Z</t>
+        </is>
+      </c>
+      <c r="D3570" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3570" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3570" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3571">
+      <c r="A3571" t="inlineStr">
+        <is>
+          <t>bb959709-4468-4fa5-91b8-c787c9d7d31b</t>
+        </is>
+      </c>
+      <c r="B3571" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3571" t="inlineStr">
+        <is>
+          <t>2026-09-15T21:18:49.217Z</t>
+        </is>
+      </c>
+      <c r="D3571" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3571" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3571" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3572">
+      <c r="A3572" t="inlineStr">
+        <is>
+          <t>f6745e43-83ea-415e-aa89-d9f10c5a2a5a</t>
+        </is>
+      </c>
+      <c r="B3572" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3572" t="inlineStr">
+        <is>
+          <t>2026-09-15T22:15:34.087Z</t>
+        </is>
+      </c>
+      <c r="D3572" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3572" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3572" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3573">
+      <c r="A3573" t="inlineStr">
+        <is>
+          <t>d379d9fa-942a-40ad-81cf-fd58098b50b6</t>
+        </is>
+      </c>
+      <c r="B3573" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3573" t="inlineStr">
+        <is>
+          <t>2026-09-15T23:35:58.793Z</t>
+        </is>
+      </c>
+      <c r="D3573" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3573" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3573" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3573"/>
+  <dimension ref="A1:F3590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88718,6 +88718,516 @@
         </is>
       </c>
     </row>
+    <row r="3574">
+      <c r="A3574" t="inlineStr">
+        <is>
+          <t>bf4472a6-c248-4288-b20f-ad56b67956ee</t>
+        </is>
+      </c>
+      <c r="B3574" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3574" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:40:52.212Z</t>
+        </is>
+      </c>
+      <c r="D3574" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3574" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3574" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3575">
+      <c r="A3575" t="inlineStr">
+        <is>
+          <t>6d247733-20ef-49e0-b24a-0875162183a3</t>
+        </is>
+      </c>
+      <c r="B3575" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3575" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:47:04.134Z</t>
+        </is>
+      </c>
+      <c r="D3575" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3575" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3575" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3576">
+      <c r="A3576" t="inlineStr">
+        <is>
+          <t>86d44789-c3e8-4ea3-86a6-6aec5f4f4def</t>
+        </is>
+      </c>
+      <c r="B3576" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3576" t="inlineStr">
+        <is>
+          <t>2026-09-16T05:52:38.919Z</t>
+        </is>
+      </c>
+      <c r="D3576" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3576" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3576" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3577">
+      <c r="A3577" t="inlineStr">
+        <is>
+          <t>52df82e2-0c04-4484-8e21-642db732daff</t>
+        </is>
+      </c>
+      <c r="B3577" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3577" t="inlineStr">
+        <is>
+          <t>2026-09-16T07:49:18.431Z</t>
+        </is>
+      </c>
+      <c r="D3577" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3577" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3577" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3578">
+      <c r="A3578" t="inlineStr">
+        <is>
+          <t>5557fa51-9161-4248-98ea-7b3a45ebccd6</t>
+        </is>
+      </c>
+      <c r="B3578" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3578" t="inlineStr">
+        <is>
+          <t>2026-09-16T08:45:08.130Z</t>
+        </is>
+      </c>
+      <c r="D3578" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3578" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3578" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3579">
+      <c r="A3579" t="inlineStr">
+        <is>
+          <t>dbf50e90-cab6-48d5-9319-c4ab418b0852</t>
+        </is>
+      </c>
+      <c r="B3579" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3579" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:47:32.433Z</t>
+        </is>
+      </c>
+      <c r="D3579" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3579" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3579" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3580">
+      <c r="A3580" t="inlineStr">
+        <is>
+          <t>c7f812ed-fbda-4d6c-8dc5-4f0bd0d7e156</t>
+        </is>
+      </c>
+      <c r="B3580" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3580" t="inlineStr">
+        <is>
+          <t>2026-09-16T14:49:43.036Z</t>
+        </is>
+      </c>
+      <c r="D3580" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3580" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3580" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3581">
+      <c r="A3581" t="inlineStr">
+        <is>
+          <t>fd94d9c6-b5cf-47c0-870e-86146825a548</t>
+        </is>
+      </c>
+      <c r="B3581" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3581" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:01:50.553Z</t>
+        </is>
+      </c>
+      <c r="D3581" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3581" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3581" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3582">
+      <c r="A3582" t="inlineStr">
+        <is>
+          <t>af16fc21-1da0-4e68-a6b9-b85a07c8f4ff</t>
+        </is>
+      </c>
+      <c r="B3582" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3582" t="inlineStr">
+        <is>
+          <t>2026-09-16T15:11:58.659Z</t>
+        </is>
+      </c>
+      <c r="D3582" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3582" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3582" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3583">
+      <c r="A3583" t="inlineStr">
+        <is>
+          <t>ce6d2c14-0163-4ec6-9bda-f1648817e12b</t>
+        </is>
+      </c>
+      <c r="B3583" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3583" t="inlineStr">
+        <is>
+          <t>2026-09-16T16:17:31.141Z</t>
+        </is>
+      </c>
+      <c r="D3583" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3583" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3583" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3584">
+      <c r="A3584" t="inlineStr">
+        <is>
+          <t>961b69f5-f2dc-45a3-9a7a-5f4b6ee96f3f</t>
+        </is>
+      </c>
+      <c r="B3584" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3584" t="inlineStr">
+        <is>
+          <t>2026-09-16T16:58:39.757Z</t>
+        </is>
+      </c>
+      <c r="D3584" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3584" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3584" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3585">
+      <c r="A3585" t="inlineStr">
+        <is>
+          <t>5d75cda2-97f7-472c-9a29-50aaade4df0d</t>
+        </is>
+      </c>
+      <c r="B3585" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3585" t="inlineStr">
+        <is>
+          <t>2026-09-16T17:24:32.584Z</t>
+        </is>
+      </c>
+      <c r="D3585" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3585" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3585" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3586">
+      <c r="A3586" t="inlineStr">
+        <is>
+          <t>4c26ecd8-912f-4a31-ab3d-dfe21a69bbde</t>
+        </is>
+      </c>
+      <c r="B3586" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3586" t="inlineStr">
+        <is>
+          <t>2026-09-16T17:52:28.814Z</t>
+        </is>
+      </c>
+      <c r="D3586" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3586" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3586" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3587">
+      <c r="A3587" t="inlineStr">
+        <is>
+          <t>02eb2028-2525-423e-85c0-e2407369a261</t>
+        </is>
+      </c>
+      <c r="B3587" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3587" t="inlineStr">
+        <is>
+          <t>2026-09-16T18:30:04.600Z</t>
+        </is>
+      </c>
+      <c r="D3587" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3587" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3587" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3588">
+      <c r="A3588" t="inlineStr">
+        <is>
+          <t>e2a826e4-d8e0-4449-8ca6-4515e1ad902c</t>
+        </is>
+      </c>
+      <c r="B3588" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3588" t="inlineStr">
+        <is>
+          <t>2026-09-16T21:56:21.320Z</t>
+        </is>
+      </c>
+      <c r="D3588" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3588" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3588" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3589">
+      <c r="A3589" t="inlineStr">
+        <is>
+          <t>86ee3156-c1ea-4523-865a-f527533376c0</t>
+        </is>
+      </c>
+      <c r="B3589" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3589" t="inlineStr">
+        <is>
+          <t>2026-09-16T22:28:34.927Z</t>
+        </is>
+      </c>
+      <c r="D3589" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3589" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3589" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3590">
+      <c r="A3590" t="inlineStr">
+        <is>
+          <t>aaf7c5a0-37fd-4722-8c51-7386c5485ad9</t>
+        </is>
+      </c>
+      <c r="B3590" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3590" t="inlineStr">
+        <is>
+          <t>2026-09-16T23:26:40.646Z</t>
+        </is>
+      </c>
+      <c r="D3590" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3590" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3590" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3590"/>
+  <dimension ref="A1:F3598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89228,6 +89228,246 @@
         </is>
       </c>
     </row>
+    <row r="3591">
+      <c r="A3591" t="inlineStr">
+        <is>
+          <t>5616ed6c-ab29-44a0-bcd6-886208e36b9d</t>
+        </is>
+      </c>
+      <c r="B3591" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3591" t="inlineStr">
+        <is>
+          <t>2026-09-17T04:12:22.023Z</t>
+        </is>
+      </c>
+      <c r="D3591" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3591" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3591" t="inlineStr">
+        <is>
+          <t>Robbery</t>
+        </is>
+      </c>
+    </row>
+    <row r="3592">
+      <c r="A3592" t="inlineStr">
+        <is>
+          <t>abc9e48b-c451-407a-b753-cb0ea70b9519</t>
+        </is>
+      </c>
+      <c r="B3592" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3592" t="inlineStr">
+        <is>
+          <t>2026-09-17T04:17:16.549Z</t>
+        </is>
+      </c>
+      <c r="D3592" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3592" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3592" t="inlineStr">
+        <is>
+          <t>Robbery</t>
+        </is>
+      </c>
+    </row>
+    <row r="3593">
+      <c r="A3593" t="inlineStr">
+        <is>
+          <t>46f1effd-c335-4414-b982-11c7af262381</t>
+        </is>
+      </c>
+      <c r="B3593" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3593" t="inlineStr">
+        <is>
+          <t>2026-09-17T15:48:21.116Z</t>
+        </is>
+      </c>
+      <c r="D3593" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3593" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3593" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3594">
+      <c r="A3594" t="inlineStr">
+        <is>
+          <t>3260c919-cac3-474a-92bd-592735cbd14b</t>
+        </is>
+      </c>
+      <c r="B3594" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3594" t="inlineStr">
+        <is>
+          <t>2026-09-17T16:29:09.261Z</t>
+        </is>
+      </c>
+      <c r="D3594" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3594" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3594" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3595">
+      <c r="A3595" t="inlineStr">
+        <is>
+          <t>87aade4e-4e8f-4e28-885a-e3dff48cb6de</t>
+        </is>
+      </c>
+      <c r="B3595" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3595" t="inlineStr">
+        <is>
+          <t>2026-09-17T17:38:15.812Z</t>
+        </is>
+      </c>
+      <c r="D3595" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3595" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3595" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3596">
+      <c r="A3596" t="inlineStr">
+        <is>
+          <t>f7661f68-9ac2-4ef6-b67a-4bb857d83b91</t>
+        </is>
+      </c>
+      <c r="B3596" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3596" t="inlineStr">
+        <is>
+          <t>2026-09-17T19:05:02.002Z</t>
+        </is>
+      </c>
+      <c r="D3596" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3596" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3596" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3597">
+      <c r="A3597" t="inlineStr">
+        <is>
+          <t>3691d9e4-1a5f-4569-be61-d709abe9ece8</t>
+        </is>
+      </c>
+      <c r="B3597" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3597" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:32:25.942Z</t>
+        </is>
+      </c>
+      <c r="D3597" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3597" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3597" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3598">
+      <c r="A3598" t="inlineStr">
+        <is>
+          <t>845864af-9922-4c80-b4e2-1552b73dbe49</t>
+        </is>
+      </c>
+      <c r="B3598" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3598" t="inlineStr">
+        <is>
+          <t>2026-09-17T21:48:36.750Z</t>
+        </is>
+      </c>
+      <c r="D3598" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3598" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3598" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3598"/>
+  <dimension ref="A1:F3608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89468,6 +89468,306 @@
         </is>
       </c>
     </row>
+    <row r="3599">
+      <c r="A3599" t="inlineStr">
+        <is>
+          <t>8ec61ed8-303b-44ac-9c53-b1269f7489dc</t>
+        </is>
+      </c>
+      <c r="B3599" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3599" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:49:15.283Z</t>
+        </is>
+      </c>
+      <c r="D3599" t="n">
+        <v>497</v>
+      </c>
+      <c r="E3599" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3599" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3600">
+      <c r="A3600" t="inlineStr">
+        <is>
+          <t>9dd5019c-3e70-4a5b-8989-12e166f32b79</t>
+        </is>
+      </c>
+      <c r="B3600" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3600" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:49:26.011Z</t>
+        </is>
+      </c>
+      <c r="D3600" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3600" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3600" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>3fb182ab-8090-40b4-a3d4-5bf31bafccc6</t>
+        </is>
+      </c>
+      <c r="B3601" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3601" t="inlineStr">
+        <is>
+          <t>2026-09-18T05:27:05.580Z</t>
+        </is>
+      </c>
+      <c r="D3601" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3601" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3601" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>5bce29aa-156c-4fc3-bb13-2a2e3deccb1d</t>
+        </is>
+      </c>
+      <c r="B3602" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3602" t="inlineStr">
+        <is>
+          <t>2026-09-18T14:21:17.016Z</t>
+        </is>
+      </c>
+      <c r="D3602" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3602" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3602" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>9d055399-2ee8-45eb-af54-3d804358bdff</t>
+        </is>
+      </c>
+      <c r="B3603" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3603" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:33:49.253Z</t>
+        </is>
+      </c>
+      <c r="D3603" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3603" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3603" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>b4df0ad5-f757-44b1-8b37-92d6b059fc35</t>
+        </is>
+      </c>
+      <c r="B3604" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3604" t="inlineStr">
+        <is>
+          <t>2026-09-18T17:20:52.766Z</t>
+        </is>
+      </c>
+      <c r="D3604" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3604" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3604" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>63533130-dec9-4d75-af2e-917d9bd6990f</t>
+        </is>
+      </c>
+      <c r="B3605" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3605" t="inlineStr">
+        <is>
+          <t>2026-09-18T18:25:58.449Z</t>
+        </is>
+      </c>
+      <c r="D3605" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3605" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3605" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>c95c2c22-3aaf-46da-95df-d96fee2e9469</t>
+        </is>
+      </c>
+      <c r="B3606" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3606" t="inlineStr">
+        <is>
+          <t>2026-09-18T21:33:25.617Z</t>
+        </is>
+      </c>
+      <c r="D3606" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3606" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3606" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>01dc2fbb-007c-49cd-ac61-0cbd552d2191</t>
+        </is>
+      </c>
+      <c r="B3607" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3607" t="inlineStr">
+        <is>
+          <t>2026-09-18T22:00:47.687Z</t>
+        </is>
+      </c>
+      <c r="D3607" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3607" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3607" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>bb5fa25a-f987-4d7f-a4da-bb87d4777893</t>
+        </is>
+      </c>
+      <c r="B3608" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3608" t="inlineStr">
+        <is>
+          <t>2026-09-18T23:20:13.654Z</t>
+        </is>
+      </c>
+      <c r="D3608" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3608" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3608" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3608"/>
+  <dimension ref="A1:F3612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89768,6 +89768,126 @@
         </is>
       </c>
     </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>2a8e4b13-be00-45cb-87cf-5a8237616447</t>
+        </is>
+      </c>
+      <c r="B3609" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3609" t="inlineStr">
+        <is>
+          <t>2026-09-19T10:31:57.722Z</t>
+        </is>
+      </c>
+      <c r="D3609" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3609" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3609" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>b412039e-6e1c-46c1-805f-432a1b13621f</t>
+        </is>
+      </c>
+      <c r="B3610" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3610" t="inlineStr">
+        <is>
+          <t>2026-09-19T21:10:13.219Z</t>
+        </is>
+      </c>
+      <c r="D3610" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3610" t="inlineStr">
+        <is>
+          <t>Agency Assist</t>
+        </is>
+      </c>
+      <c r="F3610" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>0a168770-d727-48d5-84d7-741bf4279ee5</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3611" t="inlineStr">
+        <is>
+          <t>2026-09-19T21:10:44.820Z</t>
+        </is>
+      </c>
+      <c r="D3611" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3611" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3611" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>e47a6cf9-681a-47bc-bd65-8ed78cb6dbf5</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3612" t="inlineStr">
+        <is>
+          <t>2026-09-19T22:27:52.900Z</t>
+        </is>
+      </c>
+      <c r="D3612" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3612" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3612" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3612"/>
+  <dimension ref="A1:F3619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89888,6 +89888,216 @@
         </is>
       </c>
     </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>4d3fd1be-5367-484f-aa20-c304e4968259</t>
+        </is>
+      </c>
+      <c r="B3613" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3613" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:35:29.119Z</t>
+        </is>
+      </c>
+      <c r="D3613" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3613" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3613" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>842451a3-108c-43fb-adf7-692df11b5f66</t>
+        </is>
+      </c>
+      <c r="B3614" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3614" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:41:45.800Z</t>
+        </is>
+      </c>
+      <c r="D3614" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3614" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3614" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>e1a801d8-13c8-4256-a4e5-935c4a5cae15</t>
+        </is>
+      </c>
+      <c r="B3615" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3615" t="inlineStr">
+        <is>
+          <t>2026-09-20T03:43:56.707Z</t>
+        </is>
+      </c>
+      <c r="D3615" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3615" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3615" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>56cbe608-6a1d-436f-bab7-021f42bccb98</t>
+        </is>
+      </c>
+      <c r="B3616" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3616" t="inlineStr">
+        <is>
+          <t>2026-09-20T04:12:27.125Z</t>
+        </is>
+      </c>
+      <c r="D3616" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3616" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3616" t="inlineStr">
+        <is>
+          <t>Driving Under the Influence (DUI/DWI/OWI/OVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>561f2348-fc5a-4206-8751-dce3095a618d</t>
+        </is>
+      </c>
+      <c r="B3617" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3617" t="inlineStr">
+        <is>
+          <t>2026-09-20T09:40:35.890Z</t>
+        </is>
+      </c>
+      <c r="D3617" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3617" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3617" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>c70cb4e0-65d4-4116-ba1e-f321c0e966a7</t>
+        </is>
+      </c>
+      <c r="B3618" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3618" t="inlineStr">
+        <is>
+          <t>2026-09-20T16:20:59.638Z</t>
+        </is>
+      </c>
+      <c r="D3618" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3618" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3618" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>7ead83a0-3b9f-4817-b013-389c3a44e142</t>
+        </is>
+      </c>
+      <c r="B3619" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3619" t="inlineStr">
+        <is>
+          <t>2026-09-20T17:43:52.197Z</t>
+        </is>
+      </c>
+      <c r="D3619" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3619" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3619" t="inlineStr">
+        <is>
+          <t>Destruction/Damage/Vandalism of Property</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3619"/>
+  <dimension ref="A1:F3626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90098,6 +90098,216 @@
         </is>
       </c>
     </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>069e6bb7-0c46-4b58-a1ee-a10a3514e689</t>
+        </is>
+      </c>
+      <c r="B3620" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3620" t="inlineStr">
+        <is>
+          <t>2026-09-21T06:36:30.941Z</t>
+        </is>
+      </c>
+      <c r="D3620" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3620" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3620" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>ab3385b7-f102-4f11-8311-75b22494532a</t>
+        </is>
+      </c>
+      <c r="B3621" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3621" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:53:02.173Z</t>
+        </is>
+      </c>
+      <c r="D3621" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3621" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3621" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>afb16b25-b86a-431f-9d5a-8be450f9fa59</t>
+        </is>
+      </c>
+      <c r="B3622" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3622" t="inlineStr">
+        <is>
+          <t>2026-09-21T07:55:17.356Z</t>
+        </is>
+      </c>
+      <c r="D3622" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3622" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3622" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>2b312bd4-8f6e-45f2-ae3e-01ec33f2cb1a</t>
+        </is>
+      </c>
+      <c r="B3623" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3623" t="inlineStr">
+        <is>
+          <t>2026-09-21T08:21:35.491Z</t>
+        </is>
+      </c>
+      <c r="D3623" t="n">
+        <v>512</v>
+      </c>
+      <c r="E3623" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3623" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>019df665-8c0c-4755-9ebd-607fac641c8d</t>
+        </is>
+      </c>
+      <c r="B3624" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3624" t="inlineStr">
+        <is>
+          <t>2026-09-21T08:23:20.077Z</t>
+        </is>
+      </c>
+      <c r="D3624" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3624" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3624" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>bf888768-b63c-4e9b-919d-871742621fce</t>
+        </is>
+      </c>
+      <c r="B3625" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3625" t="inlineStr">
+        <is>
+          <t>2026-09-21T08:29:09.661Z</t>
+        </is>
+      </c>
+      <c r="D3625" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3625" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3625" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>fc207d05-df73-420a-b3c2-0af24645a7f0</t>
+        </is>
+      </c>
+      <c r="B3626" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3626" t="inlineStr">
+        <is>
+          <t>2026-09-21T18:19:04.896Z</t>
+        </is>
+      </c>
+      <c r="D3626" t="n">
+        <v>541</v>
+      </c>
+      <c r="E3626" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3626" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3626"/>
+  <dimension ref="A1:F3636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90308,6 +90308,306 @@
         </is>
       </c>
     </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>404e2373-321c-4f34-9be8-5a2b680e534c</t>
+        </is>
+      </c>
+      <c r="B3627" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3627" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:50:55.141Z</t>
+        </is>
+      </c>
+      <c r="D3627" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3627" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3627" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>3fb2200c-7db5-48ee-b91f-545f13a29318</t>
+        </is>
+      </c>
+      <c r="B3628" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3628" t="inlineStr">
+        <is>
+          <t>2026-09-22T01:53:09.412Z</t>
+        </is>
+      </c>
+      <c r="D3628" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3628" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3628" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>15aea8b2-34d7-4b45-aa29-96fa40874765</t>
+        </is>
+      </c>
+      <c r="B3629" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3629" t="inlineStr">
+        <is>
+          <t>2026-09-22T06:32:43.602Z</t>
+        </is>
+      </c>
+      <c r="D3629" t="n">
+        <v>507</v>
+      </c>
+      <c r="E3629" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3629" t="inlineStr">
+        <is>
+          <t>Secured Area Access Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>d3b77471-d97f-4e0d-8f64-913829c3be04</t>
+        </is>
+      </c>
+      <c r="B3630" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3630" t="inlineStr">
+        <is>
+          <t>2026-09-22T10:49:06.216Z</t>
+        </is>
+      </c>
+      <c r="D3630" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3630" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3630" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>a79ded9c-28b0-47bf-a30a-843a484fc246</t>
+        </is>
+      </c>
+      <c r="B3631" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3631" t="inlineStr">
+        <is>
+          <t>2026-09-22T11:15:09.597Z</t>
+        </is>
+      </c>
+      <c r="D3631" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3631" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3631" t="inlineStr">
+        <is>
+          <t>Traffic Infraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>766468b7-d3f6-4dbc-adb5-507191cb1944</t>
+        </is>
+      </c>
+      <c r="B3632" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3632" t="inlineStr">
+        <is>
+          <t>2026-09-22T18:32:48.597Z</t>
+        </is>
+      </c>
+      <c r="D3632" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3632" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3632" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>e7ba7284-0a1c-4eb0-bfa2-c4cf224a3962</t>
+        </is>
+      </c>
+      <c r="B3633" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3633" t="inlineStr">
+        <is>
+          <t>2026-09-22T19:04:52.485Z</t>
+        </is>
+      </c>
+      <c r="D3633" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3633" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3633" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>7777df12-8a2a-4611-ad12-cccc358cdf91</t>
+        </is>
+      </c>
+      <c r="B3634" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3634" t="inlineStr">
+        <is>
+          <t>2026-09-22T20:26:30.160Z</t>
+        </is>
+      </c>
+      <c r="D3634" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3634" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3634" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>45799a33-0161-4e3e-a785-32f4325a6472</t>
+        </is>
+      </c>
+      <c r="B3635" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3635" t="inlineStr">
+        <is>
+          <t>2026-09-22T21:39:39.814Z</t>
+        </is>
+      </c>
+      <c r="D3635" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3635" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3635" t="inlineStr">
+        <is>
+          <t>Sex Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>e5d497d3-4d29-4c5d-95fb-d537e3b4d0f8</t>
+        </is>
+      </c>
+      <c r="B3636" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3636" t="inlineStr">
+        <is>
+          <t>2026-09-22T23:17:36.101Z</t>
+        </is>
+      </c>
+      <c r="D3636" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3636" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3636" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3636"/>
+  <dimension ref="A1:F3652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90608,6 +90608,486 @@
         </is>
       </c>
     </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>d47f70ea-1f34-46e8-bfac-3b64ac8d8d5a</t>
+        </is>
+      </c>
+      <c r="B3637" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3637" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:58:42.590Z</t>
+        </is>
+      </c>
+      <c r="D3637" t="n">
+        <v>540</v>
+      </c>
+      <c r="E3637" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3637" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>e3a96ea3-7325-476e-b3eb-6660c047c52d</t>
+        </is>
+      </c>
+      <c r="B3638" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3638" t="inlineStr">
+        <is>
+          <t>2026-09-23T05:15:02.877Z</t>
+        </is>
+      </c>
+      <c r="D3638" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3638" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3638" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>afe90142-fe69-4e3f-80eb-c61e7336b55f</t>
+        </is>
+      </c>
+      <c r="B3639" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3639" t="inlineStr">
+        <is>
+          <t>2026-09-23T11:27:52.561Z</t>
+        </is>
+      </c>
+      <c r="D3639" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3639" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3639" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>c40e025a-9216-4c7e-9815-55804da1008f</t>
+        </is>
+      </c>
+      <c r="B3640" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3640" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:58:20.649Z</t>
+        </is>
+      </c>
+      <c r="D3640" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3640" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3640" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>1d44f9d5-24e3-4d39-96fc-cb4d9f56ddfb</t>
+        </is>
+      </c>
+      <c r="B3641" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3641" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:07:06.555Z</t>
+        </is>
+      </c>
+      <c r="D3641" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3641" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3641" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>54e59e38-3ea1-42a5-8b75-e5ea50f5effe</t>
+        </is>
+      </c>
+      <c r="B3642" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3642" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:11:46.013Z</t>
+        </is>
+      </c>
+      <c r="D3642" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3642" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3642" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>72e9b825-f31c-45e9-a0b2-0e62299d175a</t>
+        </is>
+      </c>
+      <c r="B3643" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3643" t="inlineStr">
+        <is>
+          <t>2026-09-23T14:19:56.646Z</t>
+        </is>
+      </c>
+      <c r="D3643" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3643" t="inlineStr">
+        <is>
+          <t>Victim</t>
+        </is>
+      </c>
+      <c r="F3643" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>7306ef5a-4974-43cc-bfd8-b81ee1d03a86</t>
+        </is>
+      </c>
+      <c r="B3644" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3644" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:52:57.945Z</t>
+        </is>
+      </c>
+      <c r="D3644" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3644" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3644" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>d99ade76-7062-465c-b477-5e3639843ace</t>
+        </is>
+      </c>
+      <c r="B3645" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3645" t="inlineStr">
+        <is>
+          <t>2026-09-23T17:53:12.680Z</t>
+        </is>
+      </c>
+      <c r="D3645" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3645" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3645" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>d99736bc-d694-46a5-8557-7977f2145b9c</t>
+        </is>
+      </c>
+      <c r="B3646" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3646" t="inlineStr">
+        <is>
+          <t>2026-09-23T18:31:08.519Z</t>
+        </is>
+      </c>
+      <c r="D3646" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3646" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3646" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>b35ccb01-8815-4ecf-95bf-63c80ffcae0b</t>
+        </is>
+      </c>
+      <c r="B3647" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3647" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:00:44.169Z</t>
+        </is>
+      </c>
+      <c r="D3647" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3647" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3647" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>34e06075-6297-465c-97fb-baa83cef49f5</t>
+        </is>
+      </c>
+      <c r="B3648" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3648" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:01:38.426Z</t>
+        </is>
+      </c>
+      <c r="D3648" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3648" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3648" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>48196945-79ff-40e8-8bb4-e5755e367aa3</t>
+        </is>
+      </c>
+      <c r="B3649" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3649" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:05:01.611Z</t>
+        </is>
+      </c>
+      <c r="D3649" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3649" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3649" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>a27adc07-2d7f-42af-8941-9658c9073cb5</t>
+        </is>
+      </c>
+      <c r="B3650" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3650" t="inlineStr">
+        <is>
+          <t>2026-09-23T19:45:09.908Z</t>
+        </is>
+      </c>
+      <c r="D3650" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3650" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3650" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>16498b97-e940-49ab-b66f-02958886a4cc</t>
+        </is>
+      </c>
+      <c r="B3651" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3651" t="inlineStr">
+        <is>
+          <t>2026-09-23T20:17:23.630Z</t>
+        </is>
+      </c>
+      <c r="D3651" t="n">
+        <v>496</v>
+      </c>
+      <c r="E3651" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3651" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>ba35fdc9-da3f-45af-88cc-48cad4ea8bec</t>
+        </is>
+      </c>
+      <c r="B3652" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3652" t="inlineStr">
+        <is>
+          <t>2026-09-23T23:56:17.212Z</t>
+        </is>
+      </c>
+      <c r="D3652" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3652" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3652" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3652"/>
+  <dimension ref="A1:F3659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91088,6 +91088,216 @@
         </is>
       </c>
     </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>c5621183-61fd-4277-a736-6d40d423bbeb</t>
+        </is>
+      </c>
+      <c r="B3653" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3653" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:39:14.771Z</t>
+        </is>
+      </c>
+      <c r="D3653" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3653" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3653" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>107664eb-8b9b-419e-8a8d-ebb717bd79fb</t>
+        </is>
+      </c>
+      <c r="B3654" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3654" t="inlineStr">
+        <is>
+          <t>2026-09-24T16:50:42.066Z</t>
+        </is>
+      </c>
+      <c r="D3654" t="n">
+        <v>495</v>
+      </c>
+      <c r="E3654" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3654" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>35394d60-92be-4643-96cc-ca9f0e35eeb8</t>
+        </is>
+      </c>
+      <c r="B3655" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3655" t="inlineStr">
+        <is>
+          <t>2026-09-24T17:50:30.965Z</t>
+        </is>
+      </c>
+      <c r="D3655" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3655" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3655" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>041d79a7-8490-4ca9-94f3-93c6a8efc7b8</t>
+        </is>
+      </c>
+      <c r="B3656" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3656" t="inlineStr">
+        <is>
+          <t>2026-09-24T19:58:00.370Z</t>
+        </is>
+      </c>
+      <c r="D3656" t="n">
+        <v>495</v>
+      </c>
+      <c r="E3656" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3656" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>7cc4cead-cae3-4761-b4c0-973dfdc2e2e1</t>
+        </is>
+      </c>
+      <c r="B3657" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3657" t="inlineStr">
+        <is>
+          <t>2026-09-24T20:05:28.135Z</t>
+        </is>
+      </c>
+      <c r="D3657" t="n">
+        <v>495</v>
+      </c>
+      <c r="E3657" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3657" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>ba8cdf4d-ee4b-4a07-bf87-ca63265b5d48</t>
+        </is>
+      </c>
+      <c r="B3658" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3658" t="inlineStr">
+        <is>
+          <t>2026-09-24T20:13:55.988Z</t>
+        </is>
+      </c>
+      <c r="D3658" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3658" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3658" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>0d6c193c-b961-4858-be4d-81388f7d7684</t>
+        </is>
+      </c>
+      <c r="B3659" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3659" t="inlineStr">
+        <is>
+          <t>2026-09-24T21:57:37.772Z</t>
+        </is>
+      </c>
+      <c r="D3659" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3659" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3659" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3659"/>
+  <dimension ref="A1:F3662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91298,6 +91298,96 @@
         </is>
       </c>
     </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>b6ff8a7b-643d-4132-bf52-4321db85e066</t>
+        </is>
+      </c>
+      <c r="B3660" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3660" t="inlineStr">
+        <is>
+          <t>2026-09-25T15:10:20.842Z</t>
+        </is>
+      </c>
+      <c r="D3660" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3660" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3660" t="inlineStr">
+        <is>
+          <t>Homicide/Death Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>117567c8-c6bb-4599-b70a-b6ce9333d2ee</t>
+        </is>
+      </c>
+      <c r="B3661" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3661" t="inlineStr">
+        <is>
+          <t>2026-09-25T17:24:42.916Z</t>
+        </is>
+      </c>
+      <c r="D3661" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3661" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3661" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>a53b34d4-1194-4322-8100-98de73295cb4</t>
+        </is>
+      </c>
+      <c r="B3662" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3662" t="inlineStr">
+        <is>
+          <t>2026-09-25T20:04:30.653Z</t>
+        </is>
+      </c>
+      <c r="D3662" t="n">
+        <v>495</v>
+      </c>
+      <c r="E3662" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3662" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3662"/>
+  <dimension ref="A1:F3678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91388,6 +91388,486 @@
         </is>
       </c>
     </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>8f058016-1f6a-460e-a3c8-b0646ec38406</t>
+        </is>
+      </c>
+      <c r="B3663" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3663" t="inlineStr">
+        <is>
+          <t>2026-09-26T07:21:53.373Z</t>
+        </is>
+      </c>
+      <c r="D3663" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3663" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3663" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>420d24e4-9e75-4575-82f9-ad29fb1a9210</t>
+        </is>
+      </c>
+      <c r="B3664" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3664" t="inlineStr">
+        <is>
+          <t>2026-09-26T07:22:06.340Z</t>
+        </is>
+      </c>
+      <c r="D3664" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3664" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3664" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>079a6d1f-d56d-4995-9b47-75dfc4759fc9</t>
+        </is>
+      </c>
+      <c r="B3665" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3665" t="inlineStr">
+        <is>
+          <t>2026-09-26T07:37:04.547Z</t>
+        </is>
+      </c>
+      <c r="D3665" t="n">
+        <v>721</v>
+      </c>
+      <c r="E3665" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3665" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>03c70db0-59ac-4f25-ad6b-15d494977666</t>
+        </is>
+      </c>
+      <c r="B3666" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3666" t="inlineStr">
+        <is>
+          <t>2026-09-26T08:01:12.788Z</t>
+        </is>
+      </c>
+      <c r="D3666" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3666" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3666" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>63692789-7a1a-4c62-b0df-074e5a84bb50</t>
+        </is>
+      </c>
+      <c r="B3667" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3667" t="inlineStr">
+        <is>
+          <t>2026-09-26T08:07:23.181Z</t>
+        </is>
+      </c>
+      <c r="D3667" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3667" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3667" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>08d70c65-2520-40fa-9d47-1e75dd948885</t>
+        </is>
+      </c>
+      <c r="B3668" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3668" t="inlineStr">
+        <is>
+          <t>2026-09-26T09:50:44.878Z</t>
+        </is>
+      </c>
+      <c r="D3668" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3668" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3668" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>cd9dfee4-1362-4357-bd3c-8d44a6df6d94</t>
+        </is>
+      </c>
+      <c r="B3669" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3669" t="inlineStr">
+        <is>
+          <t>2026-09-26T10:09:25.711Z</t>
+        </is>
+      </c>
+      <c r="D3669" t="n">
+        <v>721</v>
+      </c>
+      <c r="E3669" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3669" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>880a1ec2-1c00-4ccb-954a-a3c86b94cb72</t>
+        </is>
+      </c>
+      <c r="B3670" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3670" t="inlineStr">
+        <is>
+          <t>2026-09-26T10:34:39.542Z</t>
+        </is>
+      </c>
+      <c r="D3670" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3670" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3670" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>e0e9deea-21bf-4e2f-babe-1467f77d8802</t>
+        </is>
+      </c>
+      <c r="B3671" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3671" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:57:54.433Z</t>
+        </is>
+      </c>
+      <c r="D3671" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3671" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3671" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>08e8e6bb-8024-418a-8019-b269620ddb3c</t>
+        </is>
+      </c>
+      <c r="B3672" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3672" t="inlineStr">
+        <is>
+          <t>2026-09-26T12:03:55.653Z</t>
+        </is>
+      </c>
+      <c r="D3672" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3672" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3672" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>820b699d-8c39-453a-a7e3-5e516037df91</t>
+        </is>
+      </c>
+      <c r="B3673" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3673" t="inlineStr">
+        <is>
+          <t>2026-09-26T18:53:16.714Z</t>
+        </is>
+      </c>
+      <c r="D3673" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3673" t="inlineStr">
+        <is>
+          <t>Investigative Lead</t>
+        </is>
+      </c>
+      <c r="F3673" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>b91fd9c0-6fa8-4864-be51-4eb73acd6619</t>
+        </is>
+      </c>
+      <c r="B3674" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3674" t="inlineStr">
+        <is>
+          <t>2026-09-26T18:56:21.872Z</t>
+        </is>
+      </c>
+      <c r="D3674" t="n">
+        <v>721</v>
+      </c>
+      <c r="E3674" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3674" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Theft/Stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>493e0080-6650-4dca-9dd5-816f54bb7a0c</t>
+        </is>
+      </c>
+      <c r="B3675" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3675" t="inlineStr">
+        <is>
+          <t>2026-09-26T19:26:35.555Z</t>
+        </is>
+      </c>
+      <c r="D3675" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3675" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3675" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>bf3f7559-765e-4b15-802e-3f9457f8b6e7</t>
+        </is>
+      </c>
+      <c r="B3676" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3676" t="inlineStr">
+        <is>
+          <t>2026-09-26T19:27:33.782Z</t>
+        </is>
+      </c>
+      <c r="D3676" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3676" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3676" t="inlineStr">
+        <is>
+          <t>Larceny/Theft Offenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>ddce0130-fe59-4d0d-a97e-5e7d6ae2c1ec</t>
+        </is>
+      </c>
+      <c r="B3677" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3677" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:17:37.187Z</t>
+        </is>
+      </c>
+      <c r="D3677" t="n">
+        <v>495</v>
+      </c>
+      <c r="E3677" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3677" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>056d6f57-3e5b-4420-8961-26091e07ec50</t>
+        </is>
+      </c>
+      <c r="B3678" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3678" t="inlineStr">
+        <is>
+          <t>2026-09-26T23:36:05.689Z</t>
+        </is>
+      </c>
+      <c r="D3678" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3678" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3678" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3678"/>
+  <dimension ref="A1:F3685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91868,6 +91868,216 @@
         </is>
       </c>
     </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>a864cb5b-28f8-488c-a785-396fdf9de8cb</t>
+        </is>
+      </c>
+      <c r="B3679" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3679" t="inlineStr">
+        <is>
+          <t>2026-09-27T00:07:03.774Z</t>
+        </is>
+      </c>
+      <c r="D3679" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3679" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3679" t="inlineStr">
+        <is>
+          <t>Missing/Endangered Person/Runaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>95c9df94-8e6d-4d14-8aa4-1235964648e0</t>
+        </is>
+      </c>
+      <c r="B3680" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3680" t="inlineStr">
+        <is>
+          <t>2026-09-27T17:02:17.779Z</t>
+        </is>
+      </c>
+      <c r="D3680" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3680" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3680" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>81744f5d-b91e-4079-86f7-898fdd8a41dd</t>
+        </is>
+      </c>
+      <c r="B3681" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3681" t="inlineStr">
+        <is>
+          <t>2026-09-27T17:06:33.235Z</t>
+        </is>
+      </c>
+      <c r="D3681" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3681" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3681" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>402c4cf5-22c1-4578-a81d-441722fb1843</t>
+        </is>
+      </c>
+      <c r="B3682" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3682" t="inlineStr">
+        <is>
+          <t>2026-09-27T17:07:18.176Z</t>
+        </is>
+      </c>
+      <c r="D3682" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3682" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3682" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>e9fb887a-bd69-400a-bbdc-967fbd7460ef</t>
+        </is>
+      </c>
+      <c r="B3683" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3683" t="inlineStr">
+        <is>
+          <t>2026-09-27T18:12:57.173Z</t>
+        </is>
+      </c>
+      <c r="D3683" t="n">
+        <v>509</v>
+      </c>
+      <c r="E3683" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3683" t="inlineStr">
+        <is>
+          <t>Assault/Battery Offenses (Domestic)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>b93d6568-e912-4d8e-b04f-15f51a8477d2</t>
+        </is>
+      </c>
+      <c r="B3684" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3684" t="inlineStr">
+        <is>
+          <t>2026-09-27T18:37:14.291Z</t>
+        </is>
+      </c>
+      <c r="D3684" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3684" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3684" t="inlineStr">
+        <is>
+          <t>Hit and Run/Car Accident</t>
+        </is>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>eb676fd2-c98c-43d3-8c6d-b1e3865cbc7f</t>
+        </is>
+      </c>
+      <c r="B3685" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3685" t="inlineStr">
+        <is>
+          <t>2026-09-27T23:51:06.202Z</t>
+        </is>
+      </c>
+      <c r="D3685" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3685" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3685" t="inlineStr">
+        <is>
+          <t>Burglary/Breaking &amp; Entering</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3685"/>
+  <dimension ref="A1:F3686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92078,6 +92078,36 @@
         </is>
       </c>
     </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>b3dc4d76-f7a4-4a52-8cb1-758ce3a92cdb</t>
+        </is>
+      </c>
+      <c r="B3686" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3686" t="inlineStr">
+        <is>
+          <t>2026-09-28T17:23:06.262Z</t>
+        </is>
+      </c>
+      <c r="D3686" t="n">
+        <v>539</v>
+      </c>
+      <c r="E3686" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3686" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master Audit.xlsx
+++ b/Master Audit.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3686"/>
+  <dimension ref="A1:F3695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92108,6 +92108,276 @@
         </is>
       </c>
     </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>be07f796-9991-4dea-a4fd-7e1beccb4c9c</t>
+        </is>
+      </c>
+      <c r="B3687" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3687" t="inlineStr">
+        <is>
+          <t>2026-09-29T01:44:12.885Z</t>
+        </is>
+      </c>
+      <c r="D3687" t="n">
+        <v>508</v>
+      </c>
+      <c r="E3687" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3687" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>a3cbc863-32fc-4c48-b85f-ce1cd77087f9</t>
+        </is>
+      </c>
+      <c r="B3688" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3688" t="inlineStr">
+        <is>
+          <t>2026-09-29T01:52:07.145Z</t>
+        </is>
+      </c>
+      <c r="D3688" t="n">
+        <v>494</v>
+      </c>
+      <c r="E3688" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3688" t="inlineStr">
+        <is>
+          <t>Drugs/Narcotics</t>
+        </is>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>2873b61c-d055-4f29-94f6-c2ff631046f9</t>
+        </is>
+      </c>
+      <c r="B3689" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3689" t="inlineStr">
+        <is>
+          <t>2026-09-29T02:02:28.899Z</t>
+        </is>
+      </c>
+      <c r="D3689" t="n">
+        <v>508</v>
+      </c>
+      <c r="E3689" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3689" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>27b9f875-4d55-484d-8ad4-039ec9a6d222</t>
+        </is>
+      </c>
+      <c r="B3690" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3690" t="inlineStr">
+        <is>
+          <t>2026-09-29T04:47:45.176Z</t>
+        </is>
+      </c>
+      <c r="D3690" t="n">
+        <v>508</v>
+      </c>
+      <c r="E3690" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3690" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>4b980c91-648a-4326-9f36-0ce4d7f99a7b</t>
+        </is>
+      </c>
+      <c r="B3691" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3691" t="inlineStr">
+        <is>
+          <t>2026-09-29T05:18:58.942Z</t>
+        </is>
+      </c>
+      <c r="D3691" t="n">
+        <v>538</v>
+      </c>
+      <c r="E3691" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3691" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>0a01538c-d4f6-4cff-bec1-15259d2384c1</t>
+        </is>
+      </c>
+      <c r="B3692" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3692" t="inlineStr">
+        <is>
+          <t>2026-09-29T05:28:20.002Z</t>
+        </is>
+      </c>
+      <c r="D3692" t="n">
+        <v>508</v>
+      </c>
+      <c r="E3692" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3692" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>c9e20088-f0de-4667-871c-68063170bad3</t>
+        </is>
+      </c>
+      <c r="B3693" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3693" t="inlineStr">
+        <is>
+          <t>2026-09-29T07:11:15.102Z</t>
+        </is>
+      </c>
+      <c r="D3693" t="n">
+        <v>508</v>
+      </c>
+      <c r="E3693" t="inlineStr">
+        <is>
+          <t>Suspect</t>
+        </is>
+      </c>
+      <c r="F3693" t="inlineStr">
+        <is>
+          <t>Wanted Person (Arrest Warrant/Fugitive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>13b1cae0-da00-467f-9ae2-2cfa5c57ea83</t>
+        </is>
+      </c>
+      <c r="B3694" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3694" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:30:39.235Z</t>
+        </is>
+      </c>
+      <c r="D3694" t="n">
+        <v>538</v>
+      </c>
+      <c r="E3694" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3694" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>1cd5bddc-a637-40f2-a8b4-585e3575043d</t>
+        </is>
+      </c>
+      <c r="B3695" t="inlineStr">
+        <is>
+          <t>***</t>
+        </is>
+      </c>
+      <c r="C3695" t="inlineStr">
+        <is>
+          <t>2026-09-29T22:00:13.126Z</t>
+        </is>
+      </c>
+      <c r="D3695" t="n">
+        <v>537</v>
+      </c>
+      <c r="E3695" t="inlineStr">
+        <is>
+          <t>Missing/ Endangered Person</t>
+        </is>
+      </c>
+      <c r="F3695" t="inlineStr">
+        <is>
+          <t>Welfare Check</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
